--- a/docs/09_haip-spec-companion.xlsx
+++ b/docs/09_haip-spec-companion.xlsx
@@ -10,7 +10,7 @@
     <sheet name="HAIP読み合わせ companion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HAIP読み合わせ companion'!$A$4:$G$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HAIP読み合わせ companion'!$A$4:$I$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,10 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
@@ -101,7 +105,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -125,6 +129,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E7F0DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F5F5EF"/>
       </patternFill>
     </fill>
@@ -140,17 +154,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00B4C6E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7F0DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -190,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -217,59 +231,77 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -637,40 +669,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HAIP 仕様書 読み合わせコンパニオン — 目次の並び順どおりに全MUST/SHOULD/MAY項目を収録</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>HAIP 仕様書 読み合わせコンパニオン — 目次順の全項目 × HAIP/OID4VCI/OID4VP 3仕様のレベル比較</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>使い方: このシートの「大見出し(濃紺)」「小見出し(薄青)」は、HAIP仕様書ページの見出しと同じ並び順です。仕様書 (https://openid.net/specs/openid4vc-high-assurance-interoperability-profile-1_0.html) をブラウザで開き、上から順にスクロールしながら本シートを併読してください。出典: HAIP draft-06(2025-11-20、Final直前版)。draft-06→Final(2025-12)差分は未検証。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
+          <t>使い方: 「大見出し(濃紺)」「小見出し(薄青)」はHAIP仕様書の見出しと同じ並び。HAIP仕様書 (https://openid.net/specs/openid4vc-high-assurance-interoperability-profile-1_0.html) を開き、上から順にスクロールしながら併読してください。HAIP=draft-06(2025-11-20)、OID4VCI=1.0-final(2025-09-16)、OID4VP=1.0-final(2025-07-10) を直接確認。draft-06→Final差分は未検証。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>凡例:  必須=MUST/REQUIRED  禁止=MUST NOT  条件付き必須=条件によりMUST  推奨=SHOULD/RECOMMENDED  非推奨=NOT RECOMMENDED  任意=MAY/OPTIONAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
+          <t>凡例:  必須=MUST/REQUIRED  禁止=MUST NOT  条件付き必須=条件によりMUST  推奨=SHOULD/RECOMMENDED  非推奨=NOT RECOMMENDED  任意=MAY/OPTIONAL  対象外=その仕様のスコープ外(発行/提示の別)  規定なし=本文で規定せずプロファイル/フォーマット仕様に委譲</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>項目名</t>
@@ -678,30 +712,42 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>レベル</t>
+          <t>HAIP</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>OID4VCI
+(素の仕様)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>OID4VP
+(素の仕様)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>概要</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>サンプル / 例</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>補足(原文の語)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>仕様書の該当見出し</t>
         </is>
@@ -718,7 +764,9 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Credential Issuance</t>
         </is>
@@ -737,32 +785,42 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>VC発行のグラントタイプ。authorization_code フローのサポートが必須。</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>grant_type=authorization_code&amp;code=SplxlO...&amp;code_verifier=dBjftJ...</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>MUST support the authorization code flow.</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Credential Issuance</t>
         </is>
       </c>
     </row>
     <row r="7" ht="57" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>クレデンシャルフォーマット 最低1種の対応</t>
         </is>
@@ -772,71 +830,91 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>SD-JWT VC・mdoc のうち少なくとも一方に対応する。</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>"format": "dc+sd-jwt"  または  "format": "mso_mdoc"</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>MUST support at least one of: IETF SD-JWT VC or ISO mdoc.</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>MUST support at least one of: IETF SD-JWT VC or ISO mdoc.(素の仕様はフォーマット非依存で任意)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Credential Issuance</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="57" customHeight="1">
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>対応フォーマットの明示(エコシステム/発行側)</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>エコシステム</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>SD-JWT VC・mdoc・両方のうちどれを必須とするかエコシステムが明示すべき。</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>(方針例)「本エコシステムでは dc+sd-jwt を必須」</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Ecosystems SHOULD clearly indicate which of these formats...required.</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Ecosystems SHOULD clearly indicate which of these formats...required.(素の仕様にエコシステム要件なし)</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Credential Issuance</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="87" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>FAPI2 Security Profile への準拠(包括要件)</t>
         </is>
@@ -846,27 +924,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>PAR・PKCE・issを含む FAPI2 Security Profile の該当条項全般に準拠する(draft-06で追加)。</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>(下記 PAR/PKCE/iss はこの包括要件の具体例)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>MUST comply with the provisions of [FAPI2 Security Profile]...This includes...PKCE, PAR...and the iss value.</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>MUST comply with the provisions of [FAPI2 Security Profile]...(素のVCIはFAPI2準拠を要求せず)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Credential Issuance</t>
         </is>
@@ -878,49 +966,61 @@
           <t>発行の起点の明示(Issuer-/Wallet-initiated)</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>エコシステム</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>発行者起点・ウォレット起点のどちら(両方)を必須とするか示す。</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>(方針例)「両方をサポート必須」</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>Ecosystems SHOULD clearly indicate whether...Issuer-initiated, Wallet-initiated...or both.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Credential Issuance</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ Issuer Metadata</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="25" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t>HAIP §Issuer Metadata</t>
         </is>
@@ -932,39 +1032,49 @@
           <t>署名付き Credential Issuer Metadata の対応</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>TLSを超える発行者認証が必要な場合、署名付きメタデータに対応する。</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>"signed_metadata": "eyJhbGciOiJFUzI1NiIsIng1YyI6WyJNSUlD..."</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>signed Credential Issuer Metadata...MUST be supported(条件付き)</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>signed metadata...MUST be supported(条件付き)。素のVCIでは signed_metadata は任意。</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>HAIP §Issuer Metadata</t>
         </is>
       </c>
     </row>
     <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>全 Credential Configuration への scope 付与</t>
         </is>
@@ -974,27 +1084,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>各 Credential Configuration にメタデータ上 scope を含める。</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>"credential_configurations_supported": { "EmployeeCredential": { "scope": "employee_credential" } }</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>metadata MUST include a scope for every Credential Configuration.</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>metadata MUST include a scope for every Credential Configuration.(素のVCIでは scope は任意)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>HAIP §Issuer Metadata</t>
         </is>
@@ -1011,34 +1131,44 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>メタデータ画像をレンダリングするウォレットは SVG・PNG 両対応。</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>"logo": { "uri": "https://issuer.example.com/logo.svg" }</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>MUST support both the SVG and PNG formats.</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>MUST support both the SVG and PNG formats.(素のVCIは画像形式を規定せず)</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>HAIP §Issuer Metadata</t>
         </is>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>画像の data URI / HTTPS URL 両対応(Wallet)</t>
         </is>
@@ -1048,27 +1178,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>画像を data URI・HTTPS URL のどちらでも取得表示できる。</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>"uri": "data:image/png;base64,iVBORw0KGgo..."</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>MUST support images...both data URIs and HTTPS URLs.</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>HAIP §Issuer Metadata</t>
         </is>
@@ -1087,42 +1227,54 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>batch_credential_issuance の有無でバッチ発行対応を明示。</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>"batch_credential_issuance": { "batch_size": 10 }</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Issuer MUST indicate whether batch issuance is supported...by including or omitting.</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>Issuer MUST indicate whether batch issuance is supported...(素のVCIでは当該metadataは任意)</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>HAIP §Issuer Metadata</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ Credential Offer</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="26" t="inlineStr">
         <is>
           <t>HAIP §Credential Offer</t>
         </is>
@@ -1141,62 +1293,82 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
           <t>エコシステム/Issuer</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>発行者起点をサポートするなら Credential Offer を用いる。</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>openid-credential-offer://?credential_offer_uri=https%3A%2F%2Fissuer.example.com%2Foffers%2F123</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>If Issuer-initiated flows are supported, they MUST use the Credential Offer.</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>If Issuer-initiated flows are supported, they MUST use the Credential Offer.(素のVCIではOffer自体が任意機構)</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>HAIP §Credential Offer</t>
         </is>
       </c>
     </row>
     <row r="19" ht="87" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>事前認可コードフロー(pre-authorized_code)</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>事前本人確認済みユーザー向けの簡易発行フロー。MUSTではない。</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>grant_type=urn:ietf:params:oauth:grant-type:pre-authorized_code&amp;pre-authorized_code=Splx...&amp;tx_code=1234</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>authorization_code フローのみ MUST。pre-authorized_code は任意併用可。</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>authorization_code のみ MUST。両仕様とも pre-authorized_code は任意併用。</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>HAIP §Credential Offer</t>
         </is>
@@ -1208,49 +1380,61 @@
           <t>haip-vci://(発行呼び出し用カスタムスキーム)</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>発行時にウォレットを起動するカスタム URL スキーム。</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>haip-vci://?credential_offer_uri=https%3A%2F%2Fissuer.example.com%2Foffers%2F123</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>the custom URL scheme haip-vci:// MAY be supported.</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>the custom URL scheme haip-vci:// MAY be supported.(HAIP固有スキーム)</t>
+        </is>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>HAIP §Credential Offer</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ Authorization Endpoint</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="26" t="inlineStr">
         <is>
           <t>HAIP §Authorization Endpoint</t>
         </is>
@@ -1267,34 +1451,44 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>認可リクエストを事前にサーバへ登録し、ブラウザ経由での改ざん・肥大化を防ぐ。</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>POST /par  →  { "request_uri": "urn:ietf:params:oauth:request_uri:6esc_11...", "expires_in": 60 }</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>FAPI2準拠の一部として必須。素のOID4VCIではRECOMMENDEDのみ。</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: FAPI2準拠の一部として必須。素のOID4VCI: Use of PAR is RECOMMENDED.</t>
+        </is>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>HAIP §Authorization Endpoint</t>
         </is>
       </c>
     </row>
     <row r="23" ht="57" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>PKCE(S256 / RFC7636)</t>
         </is>
@@ -1304,27 +1498,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>認可コード横取り攻撃を防ぐコードチャレンジ。</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>code_challenge=E9Melhoa2Ow...&amp;code_challenge_method=S256</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>FAPI2準拠の一部として必須。素のOID4VCIではRECOMMENDEDのみ。</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: FAPI2準拠の一部として必須。素のOID4VCI: it is RECOMMENDED to use PKCE.</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>HAIP §Authorization Endpoint</t>
         </is>
@@ -1341,34 +1545,44 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>認可レスポンスに認可サーバー識別子を含め出所を検証可能にする(ミックスアップ攻撃対策)。</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>Location: https://wallet.example.org/cb?code=Splx...&amp;iss=https%3A%2F%2Fissuer.example.com</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>FAPI2準拠の一部としてdraft-06で追加。draft-04には未記載。</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: FAPI2準拠の一部としてdraft-06で追加。素のOID4VCIでは iss 付与を規定せず。</t>
+        </is>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>HAIP §Authorization Endpoint</t>
         </is>
       </c>
     </row>
     <row r="25" ht="57" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>scope によるクレデンシャル種別識別</t>
         </is>
@@ -1378,50 +1592,62 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>どの種別のクレデンシャルを要求するかを scope 値で伝える。</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>GET /authorize?...&amp;scope=employee_credential</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>authorization_code フローで scope 必須。素のVCIはauthorization_detailsとの二択で任意。</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: scope必須。素のOID4VCI: scope は authorization_details との二択で任意。</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>HAIP §Authorization Endpoint</t>
         </is>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ Token Endpoint</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="26" t="inlineStr">
         <is>
           <t>HAIP §Token Endpoint</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="57" customHeight="1">
+    <row r="27" ht="72" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>DPoP(送信者制約トークン / RFC9449)</t>
@@ -1434,62 +1660,82 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>アクセストークンをウォレットの鍵に紐づけ、盗難トークンの悪用を防ぐ。</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>DPoP: eyJ0eXAiOiJkcG9wK2p3dCIsImFsZyI6IkVTMjU2IiwiandrIjp7Li4ufX0...</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>MUST support sender-constrained tokens using RFC9449。素のVCIではMAY(任意)。</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: MUST support sender-constrained tokens (RFC9449)。素のOID4VCI: DPoP nonce を MAY 提供(任意)。</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>HAIP §Token Endpoint</t>
         </is>
       </c>
     </row>
     <row r="28" ht="57" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Refresh Token の対応</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>クレデンシャル更新のため Refresh Token をサポートすることが推奨。</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>"refresh_token": "8xLOxBtZp8...", "expires_in": 86400</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>Refresh tokens are RECOMMENDED to be supported.</t>
-        </is>
-      </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: RECOMMENDED。素のOID4VCI: refresh_token は任意の OAuth 機能。</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>HAIP §Token Endpoint</t>
         </is>
@@ -1501,55 +1747,67 @@
           <t>長期経過後の Refresh Token 利用</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>非推奨</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>発行から長期間(例:1年超)経過後の refresh token 利用は推奨されない。</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>(発行から一定期間で refresh を打ち切り、再発行フローへ誘導)</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>usage of the refresh tokens is NOT RECOMMENDED(after e.g. a year).</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: NOT RECOMMENDED(after e.g. a year)。素のOID4VCIでは当該注意なし。</t>
+        </is>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>HAIP §Token Endpoint</t>
         </is>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ Token Endpoint &gt; Wallet Attestation</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-      <c r="E30" s="22" t="n"/>
-      <c r="F30" s="22" t="n"/>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="26" t="inlineStr">
         <is>
           <t>HAIP §Wallet Attestation</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="57" customHeight="1">
+    <row r="31" ht="72" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Wallet Attestation によるクライアント認証</t>
@@ -1562,32 +1820,42 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>OAuth2 エンドポイントで Wallet Attestation を用いたクライアント認証を行う。</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>OAuth-Client-Attestation: eyJ...  /  OAuth-Client-Attestation-PoP: eyJ...</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>Wallets MUST perform client authentication with the Wallet Attestation.</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: Wallets MUST perform client authentication...。素のOID4VCI: クライアント認証方式はクライアント種別依存で任意。</t>
+        </is>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>HAIP §Wallet Attestation</t>
         </is>
       </c>
     </row>
     <row r="32" ht="57" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Wallet Attestation の x5c に公開鍵証明書</t>
         </is>
@@ -1597,27 +1865,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>検証鍵(と信頼チェーン)を x5c JOSE ヘッダに含める。</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>{ "typ": "oauth-client-attestation+jwt", "alg": "ES256", "x5c": ["MIIC..."] }</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>the public key certificate...MUST be included in the x5c JOSE header.</t>
-        </is>
-      </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: x5c必須。素のOID4VCIは x5c 内包方法を規定せず(付録で鍵方式は多様)。</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>HAIP §Wallet Attestation</t>
         </is>
@@ -1629,69 +1907,89 @@
           <t>Wallet Attestation の Issuer 間再利用の禁止</t>
         </is>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>禁止</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>同一の Wallet Attestation を異なる発行者にまたいで使い回してはならない。</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>(発行者ごとに別個の Attestation を取得)</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>Wallet Attestations MUST NOT be reused across different Issuers.</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: MUST NOT be reused across different Issuers.(素のOID4VCIに当該禁止なし)</t>
+        </is>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
         <is>
           <t>HAIP §Wallet Attestation</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="72" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
+    <row r="34" ht="57" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>インスタンス固有識別子の混入禁止</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>禁止</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>個々のウォレットインスタンスを一意識別する値を含めない。sub は全インスタンス共通値。</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>"sub": "https://wallet.example.com/product/MyWalletApp"(全端末で同一)</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>MUST NOT introduce a unique identifier...sub...MUST be shared by all instances.</t>
-        </is>
-      </c>
-      <c r="G34" s="19" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: MUST NOT introduce a unique identifier...(プライバシー要件)。素のOID4VCIに当該規定なし。</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>HAIP §Wallet Attestation</t>
         </is>
@@ -1703,49 +2001,61 @@
           <t>Wallet Attestation フォーマット(Appendix E)の要求</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>エコシステム</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>相互運用を求めるなら Appendix E の Wallet Attestation 形式を要求すべき(代替はMAY)。</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>(方針例)「Wallet Attestation は HAIP Appendix E 形式を必須」</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>SHOULD require...Appendix E / MAY choose other formats.</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: SHOULD require...Appendix E。素のOID4VCIにエコシステム要件なし。</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
         <is>
           <t>HAIP §Wallet Attestation</t>
         </is>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ Credential Endpoint</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="23" t="inlineStr">
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="25" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="25" t="n"/>
+      <c r="F36" s="25" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="26" t="inlineStr">
         <is>
           <t>HAIP §Credential Endpoint</t>
         </is>
@@ -1757,123 +2067,155 @@
           <t>proof_type(jwt / attestation)</t>
         </is>
       </c>
-      <c r="B37" s="28" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>必須(両方)</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>条件付き必須</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Issuer/Wallet</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>発行時に鍵所有/鍵証明を示す proof の型。jwt(key_attestation併用)とattestationの両サポート。</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>{ "proofs": { "jwt": ["eyJ0eXAiOiJvcGVuaWQ0dmNpLXByb29mK2p3dCI..."] } }</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
-        <is>
-          <t>両方のproof typeサポートが必須。素のVCIは条件付き。</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: 両proof type必須。素のOID4VCI: proof_types_supported を示すなら proofs 必須という条件付き。</t>
+        </is>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
         <is>
           <t>HAIP §Credential Endpoint</t>
         </is>
       </c>
     </row>
     <row r="38" ht="57" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Nonce Endpoint</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>条件付き必須</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>cryptographic_binding_methods_supported があれば nonce_endpoint を公開。</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>POST /nonce  →  { "c_nonce": "wKI4LT...oi8" }</t>
         </is>
       </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>the nonce_endpoint MUST be present(条件付き)。proofのリプレイ防止用チャレンジ。</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>両仕様とも「proofにc_nonceを要求するなら MUST」。HAIPは暗号バインディング前提で実質必須。</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>HAIP §Credential Endpoint</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="57" customHeight="1">
+    <row r="39" ht="72" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>バッチ発行の利用(対応時)</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="F39" s="13" t="inlineStr">
         <is>
           <t>バッチ発行が使えるなら連続リクエストよりバッチを使うべき。</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>{ "proofs": { "jwt": ["proof1","proof2","proof3"] } }</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
-        <is>
-          <t>the Wallet SHOULD use it rather than making consecutive requests.</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: SHOULD use it rather than making consecutive requests.(素のOID4VCIに当該推奨なし)</t>
+        </is>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
         <is>
           <t>HAIP §Credential Endpoint</t>
         </is>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ Credential Endpoint &gt; Key Attestation</t>
         </is>
       </c>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
-      <c r="F40" s="22" t="n"/>
-      <c r="G40" s="23" t="inlineStr">
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="25" t="n"/>
+      <c r="D40" s="25" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="25" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="26" t="inlineStr">
         <is>
           <t>HAIP §Key Attestation</t>
         </is>
@@ -1892,32 +2234,42 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="F41" s="13" t="inlineStr">
         <is>
           <t>proof の鍵がセキュアな環境で保持されることを示す Key Attestation に対応。</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>{ "typ": "key-attestation+jwt", "attested_keys": [ {"kty":"EC","crv":"P-256",...} ] }</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
-        <is>
-          <t>Wallets MUST support key attestations.</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: Wallets MUST support key attestations。素のOID4VCI: proof は鍵証明/所有証明を選べる任意。</t>
+        </is>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
         <is>
           <t>HAIP §Key Attestation</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="57" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>Key Attestation(Appendix D)の x5c 要件</t>
         </is>
@@ -1927,27 +2279,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="F42" s="19" t="inlineStr">
         <is>
           <t>Appendix D 形式使用時、検証鍵を x5c に含める。自己署名不可・アンカー非内包。</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>{ "typ": "key-attestation+jwt", "alg": "ES256", "x5c": ["MIIC..."] }</t>
         </is>
       </c>
-      <c r="F42" s="18" t="inlineStr">
-        <is>
-          <t>MUST be included in the x5c / MUST NOT be self-signed.</t>
-        </is>
-      </c>
-      <c r="G42" s="19" t="inlineStr">
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: MUST be included in the x5c / MUST NOT be self-signed.(素のOID4VCIは形式詳細を規定せず)</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="inlineStr">
         <is>
           <t>HAIP §Key Attestation</t>
         </is>
@@ -1959,69 +2321,89 @@
           <t>バッチ時の単一 attestation への集約</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>バッチ発行で複数鍵を使う場合、全鍵を単一の Key Attestation で証明すべき。</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>"attested_keys": [ {key1}, {key2}, {key3} ](1つのattestationに集約)</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>all public keys...SHOULD be attested within a single key attestation.</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: SHOULD be attested within a single key attestation.</t>
+        </is>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>HAIP §Key Attestation</t>
         </is>
       </c>
     </row>
     <row r="44" ht="57" customHeight="1">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>Key Attestation フォーマット(Appendix D)の要求</t>
         </is>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
         <is>
           <t>エコシステム</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>鍵証明レベルの相互運用を求めるなら Appendix D 形式を要求すべき(代替はMAY)。</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>(方針例)「Key Attestation は HAIP Appendix D 形式を必須」</t>
         </is>
       </c>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>SHOULD require...Appendix D / MAY choose other formats.</t>
-        </is>
-      </c>
-      <c r="G44" s="19" t="inlineStr">
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: SHOULD require...Appendix D。素のOID4VCIにエコシステム要件なし。</t>
+        </is>
+      </c>
+      <c r="I44" s="21" t="inlineStr">
         <is>
           <t>HAIP §Key Attestation</t>
         </is>
@@ -2038,7 +2420,9 @@
       <c r="D45" s="6" t="n"/>
       <c r="E45" s="6" t="n"/>
       <c r="F45" s="6" t="n"/>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations</t>
         </is>
@@ -2055,64 +2439,84 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>VP(提示)を要求・返却するためのレスポンスタイプ。</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>response_type=vp_token</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
-        <is>
-          <t>vp_token MUST be used.</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>両仕様とも vp_token 応答時は MUST。</t>
+        </is>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="72" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="47" ht="57" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>対応フォーマットの明示(エコシステム/提示側)</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B47" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
         <is>
           <t>エコシステム</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>SD-JWT VC・mdoc・両方のうちどれを必須とするかエコシステムが明示すべき。</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>(方針例)「本エコシステムでは検証者は両フォーマット対応必須」</t>
         </is>
       </c>
-      <c r="F47" s="18" t="inlineStr">
-        <is>
-          <t>Ecosystems SHOULD clearly indicate which of these formats...required to be supported.</t>
-        </is>
-      </c>
-      <c r="G47" s="19" t="inlineStr">
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: Ecosystems SHOULD clearly indicate...(素のOID4VPにエコシステム要件なし)</t>
+        </is>
+      </c>
+      <c r="I47" s="21" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations</t>
         </is>
@@ -2129,34 +2533,44 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>提示要求を記述する専用クエリ言語。presentation_definitionは使用不可。</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>{ "credentials": [ { "id":"e","format":"dc+sd-jwt","meta":{"vct_values":[...]},"claims":[{"path":["family_name"]}] } ] }</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
-        <is>
-          <t>DCQL query and response...MUST be used。OID4VP 1.0 FinalでPE廃止。</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>両仕様とも DCQL 必須(OID4VP 1.0 Final で presentation_definition 廃止)。</t>
+        </is>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations</t>
         </is>
       </c>
     </row>
     <row r="49" ht="72" customHeight="1">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>aki ベース Trusted Authorities クエリ</t>
         </is>
@@ -2166,27 +2580,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="F49" s="19" t="inlineStr">
         <is>
           <t>発行者(トラストアンカー)を Authority Key Identifier で絞り込む DCQL 機能。</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>"trusted_authorities": [ { "type": "aki", "values": ["s9tIpPmhxdiuNkHMEWNpYim8S8Y"] } ]</t>
         </is>
       </c>
-      <c r="F49" s="18" t="inlineStr">
-        <is>
-          <t>aki-based Trusted Authority Query...MUST be supported.</t>
-        </is>
-      </c>
-      <c r="G49" s="19" t="inlineStr">
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: MUST be supported。素のOID4VP: trusted_authorities は任意の DCQL 機能。</t>
+        </is>
+      </c>
+      <c r="I49" s="21" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations</t>
         </is>
@@ -2203,44 +2627,56 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Verifier</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>レスポンス暗号化の公開鍵をリクエストごとに使い捨てにする。</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>"client_metadata": { "jwks": { "keys": [ {"kty":"EC","use":"enc","crv":"P-256",...} ] } }</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
-        <is>
-          <t>Verifiers MUST supply ephemeral encryption public keys specific to each request.</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: MUST supply ephemeral encryption keys per request。素のOID4VPでは必須化せず。</t>
+        </is>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations</t>
         </is>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="21" t="inlineStr">
+      <c r="A51" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ OpenID for Verifiable Presentations via Redirects</t>
         </is>
       </c>
-      <c r="B51" s="22" t="n"/>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="22" t="n"/>
-      <c r="F51" s="22" t="n"/>
-      <c r="G51" s="23" t="inlineStr">
+      <c r="B51" s="25" t="n"/>
+      <c r="C51" s="25" t="n"/>
+      <c r="D51" s="25" t="n"/>
+      <c r="E51" s="25" t="n"/>
+      <c r="F51" s="25" t="n"/>
+      <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
+      <c r="I51" s="26" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
@@ -2257,34 +2693,44 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>提示レスポンスを Verifier サーバへ直接POSTし、JWE暗号化する応答モード。</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>response_mode=direct_post.jwt</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
-        <is>
-          <t>Response encryption MUST be used by utilizing response mode direct_post.jwt.</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: MUST。素のOID4VP: fragment/direct_post/direct_post.jwt/dc_api.jwt から選択可。</t>
+        </is>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
       </c>
     </row>
     <row r="53" ht="72" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>レスポンス暗号化(JWE: ECDH-ES + enc)</t>
         </is>
@@ -2294,27 +2740,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>VPトークンをVerifierの公開鍵宛に暗号化。ECDH-ES必須、encはA128GCM/A256GCM。</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>{ "alg": "ECDH-ES", "enc": "A256GCM", "epk": { "kty":"EC","crv":"P-256",... } }</t>
         </is>
       </c>
-      <c r="F53" s="18" t="inlineStr">
-        <is>
-          <t>ECDH-ES MUST be supported。VerifierはA128GCM/A256GCM両方MUST、両対応時はA256GCM推奨(SHOULD)。</t>
-        </is>
-      </c>
-      <c r="G53" s="19" t="inlineStr">
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: ECDH-ES必須・両GCM対応。素のOID4VP: 暗号化は任意(enc デフォルト A128GCM)。</t>
+        </is>
+      </c>
+      <c r="I53" s="21" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
@@ -2326,39 +2782,49 @@
           <t>client_id プレフィックス = x509_hash</t>
         </is>
       </c>
-      <c r="B54" s="28" t="inlineStr">
+      <c r="B54" s="32" t="inlineStr">
         <is>
           <t>必須(x509_hashのみ)</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="F54" s="13" t="inlineStr">
         <is>
           <t>Verifierの身元識別方式。x509_hashは証明書ハッシュで識別。</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="G54" s="14" t="inlineStr">
         <is>
           <t>client_id=x509_hash:Uvcpq0Yn6...gAsr8B</t>
         </is>
       </c>
-      <c r="F54" s="13" t="inlineStr">
-        <is>
-          <t>Client Identifier Prefix x509_hash MUST use and accept。draft-04でx509_san_dns廃止。</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: x509_hash のみ必須。素のOID4VP: 複数プレフィックス(redirect_uri/x509_san_dns/did等)から選択可。</t>
+        </is>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
       </c>
     </row>
     <row r="55" ht="72" customHeight="1">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>署名付きリクエスト(JAR / RFC9101)</t>
         </is>
@@ -2368,27 +2834,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D55" s="33" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="F55" s="19" t="inlineStr">
         <is>
           <t>認可リクエストを署名付きJWT(request_uri参照渡し)にする。</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
         <is>
           <t>request_uri=https%3A%2F%2Fverifier.example.com%2Freq%2F5Fd  →  ヘッダ { "alg":"ES256","x5c":["MIID..."] }</t>
         </is>
       </c>
-      <c r="F55" s="18" t="inlineStr">
-        <is>
-          <t>Signed Authorization Requests MUST be used by utilizing JAR.</t>
-        </is>
-      </c>
-      <c r="G55" s="19" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: JAR必須。素のOID4VP: 署名可否は client_id プレフィックス依存(x509系は署名必須/redirect_uriは不可)。</t>
+        </is>
+      </c>
+      <c r="I55" s="21" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
@@ -2405,64 +2881,84 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>同一端末内でのリダイレクト提示フローに両者が対応する。</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>openid4vp://?client_id=x509_hash%3A...&amp;request_uri=https%3A%2F%2Fverifier.example.com%2Freq%2F5Fd</t>
         </is>
       </c>
-      <c r="F56" s="13" t="inlineStr">
-        <is>
-          <t>MUST support the 'same-device' flow.</t>
-        </is>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: MUST support the 'same-device' flow.(素のOID4VPは両フロー記述するが必須化せず)</t>
+        </is>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="15" t="inlineStr">
+    <row r="57" ht="57" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>same-device フローのみ利用</t>
         </is>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B57" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
         <is>
           <t>Verifier</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="F57" s="19" t="inlineStr">
         <is>
           <t>検証者は原則 same-device フローのみを使うことが推奨される。</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>(cross-device特有のリスクがある場合を除き same-deviceのみ提供)</t>
         </is>
       </c>
-      <c r="F57" s="18" t="inlineStr">
-        <is>
-          <t>RECOMMENDED to use only the 'same-device' flow.</t>
-        </is>
-      </c>
-      <c r="G57" s="19" t="inlineStr">
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: RECOMMENDED to use only the 'same-device' flow.</t>
+        </is>
+      </c>
+      <c r="I57" s="21" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
@@ -2479,81 +2975,103 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="F58" s="13" t="inlineStr">
         <is>
           <t>検証者は応答に redirect_uri を含め、ウォレットは追従。戻らなければ提示を拒否。</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>{ "redirect_uri": "https://verifier.example.com/cb?response_code=091535f6..." }</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
-        <is>
-          <t>MUST include redirect_uri / MUST follow / MUST reject if not followed.</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr">
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: MUST include/follow/reject。素のOID4VP: direct_post時の redirect_uri は任意。</t>
+        </is>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
       </c>
     </row>
     <row r="59" ht="72" customHeight="1">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>haip-vp://(提示呼び出し用カスタムスキーム)</t>
         </is>
       </c>
-      <c r="B59" s="25" t="inlineStr">
+      <c r="B59" s="28" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C59" s="16" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="F59" s="19" t="inlineStr">
         <is>
           <t>提示時にウォレットを起動するカスタム URL スキーム。</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="G59" s="14" t="inlineStr">
         <is>
           <t>haip-vp://?client_id=x509_hash%3A...&amp;request_uri=https%3A%2F%2Fverifier.example.com%2Freq%2F5Fd</t>
         </is>
       </c>
-      <c r="F59" s="18" t="inlineStr">
-        <is>
-          <t>the custom URL scheme haip-vp:// MAY be supported.</t>
-        </is>
-      </c>
-      <c r="G59" s="19" t="inlineStr">
+      <c r="H59" s="20" t="inlineStr">
+        <is>
+          <t>the custom URL scheme haip-vp:// MAY be supported.(HAIP固有スキーム)</t>
+        </is>
+      </c>
+      <c r="I59" s="21" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="21" t="inlineStr">
+      <c r="A60" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ OpenID for Verifiable Presentations via W3C Digital Credentials API</t>
         </is>
       </c>
-      <c r="B60" s="22" t="n"/>
-      <c r="C60" s="22" t="n"/>
-      <c r="D60" s="22" t="n"/>
-      <c r="E60" s="22" t="n"/>
-      <c r="F60" s="22" t="n"/>
-      <c r="G60" s="23" t="inlineStr">
+      <c r="B60" s="25" t="n"/>
+      <c r="C60" s="25" t="n"/>
+      <c r="D60" s="25" t="n"/>
+      <c r="E60" s="25" t="n"/>
+      <c r="F60" s="25" t="n"/>
+      <c r="G60" s="25" t="n"/>
+      <c r="H60" s="25" t="n"/>
+      <c r="I60" s="26" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via W3C Digital Credentials API</t>
         </is>
@@ -2565,49 +3083,61 @@
           <t>DC API 経由の OID4VP(response_mode=dc_api.jwt)</t>
         </is>
       </c>
-      <c r="B61" s="28" t="inlineStr">
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>必須(DC API利用時)</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>ブラウザ/OSのDigital Credentials API経由でやり取りする経路。</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>navigator.credentials.get({ digital: { requests: [ { protocol:"openid4vp", data:{...} } ] } })</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
-        <is>
-          <t>response Mode MUST be dc_api.jwt。素のVPではDC APIはリダイレクトと並列の任意選択肢。</t>
-        </is>
-      </c>
-      <c r="G61" s="14" t="inlineStr">
+      <c r="H61" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: DC API利用時は dc_api.jwt 必須。素のOID4VP: DC API はリダイレクトと並列の任意選択肢。</t>
+        </is>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
         <is>
           <t>HAIP §OpenID for Verifiable Presentations via W3C Digital Credentials API</t>
         </is>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="21" t="inlineStr">
+      <c r="A62" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　▸ Requirements specific to Credential Formats(提示時)</t>
         </is>
       </c>
-      <c r="B62" s="22" t="n"/>
-      <c r="C62" s="22" t="n"/>
-      <c r="D62" s="22" t="n"/>
-      <c r="E62" s="22" t="n"/>
-      <c r="F62" s="22" t="n"/>
-      <c r="G62" s="23" t="inlineStr">
+      <c r="B62" s="25" t="n"/>
+      <c r="C62" s="25" t="n"/>
+      <c r="D62" s="25" t="n"/>
+      <c r="E62" s="25" t="n"/>
+      <c r="F62" s="25" t="n"/>
+      <c r="G62" s="25" t="n"/>
+      <c r="H62" s="25" t="n"/>
+      <c r="I62" s="26" t="inlineStr">
         <is>
           <t>HAIP §Requirements specific to Credential Formats</t>
         </is>
@@ -2624,34 +3154,44 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D63" s="33" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Wallet/Verifier</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="F63" s="13" t="inlineStr">
         <is>
           <t>提示時にHolderが秘密鍵でnonce/aud/sd_hashに署名し持ち主を証明。</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="G63" s="14" t="inlineStr">
         <is>
           <t>~eyJ0eXAiOiJrYitqd3QiLCJhbGciOiJFUzI1NiJ9.eyJub25jZSI6Im4tMFM2Iiwi...</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
-        <is>
-          <t>KB-JWT...MUST always be present when presenting an SD-JWT VC.</t>
-        </is>
-      </c>
-      <c r="G63" s="14" t="inlineStr">
+      <c r="H63" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: SD-JWT VC提示時は常時必須。SD-JWT VC仕様: holder binding時に必要。</t>
+        </is>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>HAIP §IETF SD-JWT VC</t>
         </is>
       </c>
     </row>
     <row r="64" ht="57" customHeight="1">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>mdoc: intent_to_retain パラメータ</t>
         </is>
@@ -2661,27 +3201,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D64" s="33" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
         <is>
           <t>Verifier</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>DCQLのmdocクエリに intent_to_retain を含める。</t>
         </is>
       </c>
-      <c r="E64" s="12" t="inlineStr">
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>{ "path": ["org.iso.18013.5.1", "given_name"], "intent_to_retain": false }</t>
         </is>
       </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>intent_to_retain パラメータがMUSTで存在。</t>
-        </is>
-      </c>
-      <c r="G64" s="19" t="inlineStr">
+      <c r="H64" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: MUSTで存在。素のOID4VP: mdoc利用時のDCQLパラメータ。</t>
+        </is>
+      </c>
+      <c r="I64" s="21" t="inlineStr">
         <is>
           <t>HAIP §ISO Mobile Documents</t>
         </is>
@@ -2698,27 +3248,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="F65" s="13" t="inlineStr">
         <is>
           <t>複数mdocを提示する場合、各々別個の DeviceResponse として返却。</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="G65" s="14" t="inlineStr">
         <is>
           <t>vp_token: { "cred1": ["&lt;DeviceResponse1&gt;"], "cred2": ["&lt;DeviceResponse2&gt;"] }</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
-        <is>
-          <t>each mdoc MUST be returned as a separate DeviceResponse instance.</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="H65" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: each mdoc MUST be a separate DeviceResponse.(ISO mdoc仕様側の詳細)</t>
+        </is>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
         <is>
           <t>HAIP §ISO Mobile Documents</t>
         </is>
@@ -2735,7 +3295,9 @@
       <c r="D66" s="6" t="n"/>
       <c r="E66" s="6" t="n"/>
       <c r="F66" s="6" t="n"/>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="6" t="n"/>
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>HAIP §IETF SD-JWT VC Profile</t>
         </is>
@@ -2752,34 +3314,44 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>Issuer/Wallet/Verifier</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>SD-JWT VC は Compact serialization(~区切り文字列)に対応する。JSON serialization は任意。</t>
         </is>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>eyJ0eXAiOiJkYytzZC1qd3QiLCJhbGciOiJFUzI1NiJ9.eyJfc2QiOls...~WyJfMjZi...~</t>
         </is>
       </c>
-      <c r="F67" s="13" t="inlineStr">
-        <is>
-          <t>Compact serialization MUST be supported.(JSON serialization は MAY)</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="inlineStr">
+      <c r="H67" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: Compact serialization MUST。素のOID4VCI/VPはフォーマット内部を規定せず(委譲)。</t>
+        </is>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
         <is>
           <t>HAIP §IETF SD-JWT VC Profile</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="15" t="inlineStr">
+    <row r="68" ht="57" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>iss クレームの HTTPS URL 必須</t>
         </is>
@@ -2789,27 +3361,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C68" s="16" t="inlineStr">
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr">
         <is>
           <t>iss クレームが存在する場合、HTTPS URL である。</t>
         </is>
       </c>
-      <c r="E68" s="12" t="inlineStr">
+      <c r="G68" s="14" t="inlineStr">
         <is>
           <t>"iss": "https://issuer.example.com"</t>
         </is>
       </c>
-      <c r="F68" s="18" t="inlineStr">
-        <is>
-          <t>The iss claim, if present, MUST be an HTTPS URL.</t>
-        </is>
-      </c>
-      <c r="G68" s="19" t="inlineStr">
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: The iss claim, if present, MUST be an HTTPS URL.(フォーマット仕様への上乗せ)</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
         <is>
           <t>HAIP §Issuer identification and key resolution</t>
         </is>
@@ -2826,70 +3408,90 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D69" s="11" t="inlineStr">
+      <c r="F69" s="13" t="inlineStr">
         <is>
           <t>SD-JWT VCの署名検証鍵をx5cの証明書チェーンで提供(JWKS問い合わせ不要)。</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>{ "typ": "dc+sd-jwt", "alg": "ES256", "x5c": ["MIIDVerifierCert...", "MIIDIntermediate..."] }</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr">
-        <is>
-          <t>唯一の必須鍵解決メカニズム。自己署名不可・トラストアンカー非内包。</t>
-        </is>
-      </c>
-      <c r="G69" s="14" t="inlineStr">
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: X.509 が唯一の必須鍵解決。素のOID4VCI/VPは鍵解決方式に中立。</t>
+        </is>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
         <is>
           <t>HAIP §Issuer identification and key resolution</t>
         </is>
       </c>
     </row>
     <row r="70" ht="57" customHeight="1">
-      <c r="A70" s="15" t="inlineStr">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t>cnf.jwk による Holder Binding 鍵提供</t>
         </is>
       </c>
-      <c r="B70" s="28" t="inlineStr">
+      <c r="B70" s="32" t="inlineStr">
         <is>
           <t>必須(該当時)</t>
         </is>
       </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="F70" s="19" t="inlineStr">
         <is>
           <t>cryptographic holder bindingが必須な場合、cnf.jwkにJWKを含める。</t>
         </is>
       </c>
-      <c r="E70" s="12" t="inlineStr">
+      <c r="G70" s="14" t="inlineStr">
         <is>
           <t>"cnf": { "jwk": { "kty":"EC","crv":"P-256","x":"...","y":"..." } }</t>
         </is>
       </c>
-      <c r="F70" s="18" t="inlineStr">
-        <is>
-          <t>MUST include JSON Web Key in jwk if holder binding required.</t>
-        </is>
-      </c>
-      <c r="G70" s="19" t="inlineStr">
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: MUST include JWK in jwk if holder binding required.</t>
+        </is>
+      </c>
+      <c r="I70" s="21" t="inlineStr">
         <is>
           <t>HAIP §Cryptographic Holder Binding between VC and VP</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="87" customHeight="1">
+    <row r="71" ht="72" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
           <t>有効期間表現(exp / status / 両方)</t>
@@ -2900,64 +3502,84 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
         <is>
           <t>Issuer/Wallet/Verifier</t>
         </is>
       </c>
-      <c r="D71" s="11" t="inlineStr">
+      <c r="F71" s="13" t="inlineStr">
         <is>
           <t>有効期間を設ける場合、exp・status・両方のいずれかを用いる。WalletとVerifierは両対応。</t>
         </is>
       </c>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>"exp": 1769817600   または   "status": { "status_list": { "idx": 412, "uri": "..." } }</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr">
-        <is>
-          <t>the Issuer MUST use an exp claim, a status claim, or both. Wallet and Verifier MUST support both mechanisms.</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="inlineStr">
+      <c r="H71" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: MUST use exp/status/both; Wallet &amp; Verifier MUST support both.</t>
+        </is>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
         <is>
           <t>HAIP §IETF SD-JWT VC Profile</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="42" customHeight="1">
-      <c r="A72" s="15" t="inlineStr">
+    <row r="72" ht="57" customHeight="1">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t>SD-JWT VC 有効期間の制限</t>
         </is>
       </c>
-      <c r="B72" s="20" t="inlineStr">
+      <c r="B72" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="C72" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>SD-JWT VC 発行時は有効期間を制限することが推奨される。</t>
         </is>
       </c>
-      <c r="E72" s="12" t="inlineStr">
+      <c r="G72" s="14" t="inlineStr">
         <is>
           <t>"iat": 1767225600, "exp": 1769817600(約30日)</t>
         </is>
       </c>
-      <c r="F72" s="18" t="inlineStr">
-        <is>
-          <t>RECOMMENDED that Issuers limit the validity period.</t>
-        </is>
-      </c>
-      <c r="G72" s="19" t="inlineStr">
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: RECOMMENDED that Issuers limit the validity period.</t>
+        </is>
+      </c>
+      <c r="I72" s="21" t="inlineStr">
         <is>
           <t>HAIP §IETF SD-JWT VC Profile</t>
         </is>
@@ -2974,34 +3596,44 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D73" s="11" t="inlineStr">
+      <c r="F73" s="13" t="inlineStr">
         <is>
           <t>各クレデンシャルに固有で予測不能な status list インデックスを割り当てる。</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>"status": { "status_list": { "idx": 293857, "uri": "https://issuer.example.com/statuslists/1" } }</t>
         </is>
       </c>
-      <c r="F73" s="13" t="inlineStr">
-        <is>
-          <t>Each Credential MUST have its own unique, unpredictable status list index.</t>
-        </is>
-      </c>
-      <c r="G73" s="14" t="inlineStr">
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: MUST have its own unique, unpredictable status list index.(プライバシー)</t>
+        </is>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
         <is>
           <t>HAIP §IETF SD-JWT VC Profile</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="87" customHeight="1">
-      <c r="A74" s="15" t="inlineStr">
+    <row r="74" ht="57" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>Status List Token の署名鍵を x5c に明記</t>
         </is>
@@ -3011,27 +3643,37 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C74" s="16" t="inlineStr">
+      <c r="C74" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>Status List Token自体の署名検証用公開鍵をx5cに含める。</t>
         </is>
       </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="G74" s="14" t="inlineStr">
         <is>
           <t>{ "typ": "statuslist+jwt", "alg": "ES256", "x5c": ["MIIC..."] }</t>
         </is>
       </c>
-      <c r="F74" s="18" t="inlineStr">
-        <is>
-          <t>The public key used to validate the signature on the Status List Token MUST be included in the x5c JOSE header.</t>
-        </is>
-      </c>
-      <c r="G74" s="19" t="inlineStr">
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: public key...MUST be included in the x5c JOSE header.</t>
+        </is>
+      </c>
+      <c r="I74" s="21" t="inlineStr">
         <is>
           <t>HAIP §IETF SD-JWT VC Profile</t>
         </is>
@@ -3048,7 +3690,9 @@
       <c r="D75" s="6" t="n"/>
       <c r="E75" s="6" t="n"/>
       <c r="F75" s="6" t="n"/>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="6" t="n"/>
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>HAIP §Crypto Suites</t>
         </is>
@@ -3065,64 +3709,84 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D76" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>Issuer/Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D76" s="11" t="inlineStr">
+      <c r="F76" s="13" t="inlineStr">
         <is>
           <t>全エンティティが署名操作で最低限 ES256(COSE -7/-9)をサポート。</t>
         </is>
       </c>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="G76" s="14" t="inlineStr">
         <is>
           <t>{ "alg": "ES256" }   /   COSE alg: -7</t>
         </is>
       </c>
-      <c r="F76" s="13" t="inlineStr">
-        <is>
-          <t>MUST, at a minimum, support ECDSA with P-256 and SHA-256 (ES256).</t>
-        </is>
-      </c>
-      <c r="G76" s="14" t="inlineStr">
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: MUST, at a minimum, support ES256。素のOID4VCI/VPはアルゴリズムをプロファイルに委譲(規定なし)。</t>
+        </is>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
         <is>
           <t>HAIP §Crypto Suites</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="72" customHeight="1">
-      <c r="A77" s="15" t="inlineStr">
+    <row r="77" ht="57" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t>併用アルゴリズムの metadata 明示</t>
         </is>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B77" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C77" s="16" t="inlineStr">
+      <c r="C77" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D77" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
         <is>
           <t>各エンティティ</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="F77" s="19" t="inlineStr">
         <is>
           <t>他の暗号スイート併用時、対応アルゴリズム・鍵種別を metadata で明示すべき。</t>
         </is>
       </c>
-      <c r="E77" s="12" t="inlineStr">
+      <c r="G77" s="14" t="inlineStr">
         <is>
           <t>"credential_signing_alg_values_supported": ["ES256","ES384"]</t>
         </is>
       </c>
-      <c r="F77" s="18" t="inlineStr">
-        <is>
-          <t>each entity SHOULD make it explicit in its metadata which other algorithms and key types are supported.</t>
-        </is>
-      </c>
-      <c r="G77" s="19" t="inlineStr">
+      <c r="H77" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: SHOULD make it explicit in its metadata which other algorithms...</t>
+        </is>
+      </c>
+      <c r="I77" s="21" t="inlineStr">
         <is>
           <t>HAIP §Crypto Suites</t>
         </is>
@@ -3139,7 +3803,9 @@
       <c r="D78" s="6" t="n"/>
       <c r="E78" s="6" t="n"/>
       <c r="F78" s="6" t="n"/>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="6" t="n"/>
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>HAIP §Hash Algorithms</t>
         </is>
@@ -3156,64 +3822,84 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C79" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D79" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
         <is>
           <t>全エンティティ</t>
         </is>
       </c>
-      <c r="D79" s="11" t="inlineStr">
+      <c r="F79" s="13" t="inlineStr">
         <is>
           <t>SD-JWT VC・mdocのダイジェスト生成/検証にSHA-256を用いる。</t>
         </is>
       </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="G79" s="14" t="inlineStr">
         <is>
           <t>"_sd_alg": "sha-256"</t>
         </is>
       </c>
-      <c r="F79" s="13" t="inlineStr">
-        <is>
-          <t>The hash algorithm SHA-256 MUST be supported by all the entities.</t>
-        </is>
-      </c>
-      <c r="G79" s="14" t="inlineStr">
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: SHA-256 MUST be supported by all the entities。素のOID4VCI/VPは規定なし(委譲)。</t>
+        </is>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
         <is>
           <t>HAIP §Hash Algorithms</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="72" customHeight="1">
-      <c r="A80" s="15" t="inlineStr">
+    <row r="80" ht="57" customHeight="1">
+      <c r="A80" s="17" t="inlineStr">
         <is>
           <t>併用ハッシュの metadata 明示</t>
         </is>
       </c>
-      <c r="B80" s="20" t="inlineStr">
+      <c r="B80" s="22" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
       </c>
-      <c r="C80" s="16" t="inlineStr">
+      <c r="C80" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
         <is>
           <t>各エンティティ</t>
         </is>
       </c>
-      <c r="D80" s="17" t="inlineStr">
+      <c r="F80" s="19" t="inlineStr">
         <is>
           <t>他ハッシュ併用時、対応ハッシュをmetadataで明示すべき。</t>
         </is>
       </c>
-      <c r="E80" s="12" t="inlineStr">
+      <c r="G80" s="14" t="inlineStr">
         <is>
           <t>(metadataで対応ハッシュを列挙)</t>
         </is>
       </c>
-      <c r="F80" s="18" t="inlineStr">
-        <is>
-          <t>each entity SHOULD make it explicit in its metadata which other algorithms are supported.</t>
-        </is>
-      </c>
-      <c r="G80" s="19" t="inlineStr">
+      <c r="H80" s="20" t="inlineStr">
+        <is>
+          <t>HAIP: SHOULD make it explicit in its metadata which other algorithms...</t>
+        </is>
+      </c>
+      <c r="I80" s="21" t="inlineStr">
         <is>
           <t>HAIP §Hash Algorithms</t>
         </is>
@@ -3225,32 +3911,42 @@
           <t>追加ハッシュアルゴリズムの mandate</t>
         </is>
       </c>
-      <c r="B81" s="25" t="inlineStr">
+      <c r="B81" s="28" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
         <is>
           <t>エコシステム</t>
         </is>
       </c>
-      <c r="D81" s="11" t="inlineStr">
+      <c r="F81" s="13" t="inlineStr">
         <is>
           <t>エコシステム固有プロファイルでSHA-256以外を追加必須化してもよい。</t>
         </is>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="G81" s="14" t="inlineStr">
         <is>
           <t>(方針例)「SHA-384を追加で必須化」</t>
         </is>
       </c>
-      <c r="F81" s="13" t="inlineStr">
-        <is>
-          <t>Ecosystem-specific profiles of this specification MAY mandate additional hashing algorithms.</t>
-        </is>
-      </c>
-      <c r="G81" s="14" t="inlineStr">
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: Ecosystem-specific profiles...MAY mandate additional hashing algorithms.</t>
+        </is>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
         <is>
           <t>HAIP §Hash Algorithms</t>
         </is>
@@ -3267,13 +3963,15 @@
       <c r="D82" s="6" t="n"/>
       <c r="E82" s="6" t="n"/>
       <c r="F82" s="6" t="n"/>
-      <c r="G82" s="7" t="inlineStr">
+      <c r="G82" s="6" t="n"/>
+      <c r="H82" s="6" t="n"/>
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>HAIP §Privacy Considerations</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="57" customHeight="1">
+    <row r="83" ht="72" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
           <t>Wallet Attestation バックエンドのプライバシー設計</t>
@@ -3284,135 +3982,145 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="C83" s="23" t="inlineStr">
+        <is>
+          <t>規定なし</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
         <is>
           <t>Wallet Provider</t>
         </is>
       </c>
-      <c r="D83" s="11" t="inlineStr">
+      <c r="F83" s="13" t="inlineStr">
         <is>
           <t>Attestationを発行するバックエンドは利用者プライバシーを考慮して設計する。</t>
         </is>
       </c>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="G83" s="14" t="inlineStr">
         <is>
           <t>(バックエンドが利用状況を収集・追跡しない設計)</t>
         </is>
       </c>
-      <c r="F83" s="13" t="inlineStr">
-        <is>
-          <t>Such a backend service MUST be designed considering the privacy of its users.</t>
-        </is>
-      </c>
-      <c r="G83" s="14" t="inlineStr">
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>HAIP: Such a backend service MUST be designed considering the privacy of its users.</t>
+        </is>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
         <is>
           <t>HAIP §Privacy Considerations</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G83"/>
+  <autoFilter ref="A4:I83"/>
   <mergeCells count="19">
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/09_haip-spec-companion.xlsx
+++ b/docs/09_haip-spec-companion.xlsx
@@ -204,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -281,6 +281,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1335,14 +1338,14 @@
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
           <t>対象外</t>
@@ -1355,7 +1358,7 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>事前本人確認済みユーザー向けの簡易発行フロー。MUSTではない。</t>
+          <t>事前本人確認済みユーザー向けの簡易発行フロー。HAIP のプロファイル対象外。</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1365,7 +1368,7 @@
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>authorization_code のみ MUST。両仕様とも pre-authorized_code は任意併用。</t>
+          <t>HAIP は本文に pre-authorized_code の言及がなく authorization code flow のみをプロファイル(=対象外)。素の OID4VCI では任意で利用可。</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -1380,7 +1383,7 @@
           <t>haip-vci://(発行呼び出し用カスタムスキーム)</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -1451,7 +1454,7 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
@@ -1498,7 +1501,7 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>推奨</t>
         </is>
@@ -1747,7 +1750,7 @@
           <t>長期経過後の Refresh Token 利用</t>
         </is>
       </c>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>非推奨</t>
         </is>
@@ -1907,7 +1910,7 @@
           <t>Wallet Attestation の Issuer 間再利用の禁止</t>
         </is>
       </c>
-      <c r="B33" s="31" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>禁止</t>
         </is>
@@ -1954,7 +1957,7 @@
           <t>インスタンス固有識別子の混入禁止</t>
         </is>
       </c>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>禁止</t>
         </is>
@@ -2067,12 +2070,12 @@
           <t>proof_type(jwt / attestation)</t>
         </is>
       </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>必須(両方)</t>
         </is>
       </c>
-      <c r="C37" s="33" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -2119,7 +2122,7 @@
           <t>条件付き必須</t>
         </is>
       </c>
-      <c r="C38" s="33" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -2444,7 +2447,7 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="D46" s="34" t="inlineStr">
+      <c r="D46" s="35" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -2538,7 +2541,7 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -2782,7 +2785,7 @@
           <t>client_id プレフィックス = x509_hash</t>
         </is>
       </c>
-      <c r="B54" s="32" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>必須(x509_hashのみ)</t>
         </is>
@@ -2839,7 +2842,7 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="D55" s="33" t="inlineStr">
+      <c r="D55" s="34" t="inlineStr">
         <is>
           <t>条件付き</t>
         </is>
@@ -3017,7 +3020,7 @@
           <t>haip-vp://(提示呼び出し用カスタムスキーム)</t>
         </is>
       </c>
-      <c r="B59" s="28" t="inlineStr">
+      <c r="B59" s="29" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -3083,7 +3086,7 @@
           <t>DC API 経由の OID4VP(response_mode=dc_api.jwt)</t>
         </is>
       </c>
-      <c r="B61" s="32" t="inlineStr">
+      <c r="B61" s="33" t="inlineStr">
         <is>
           <t>必須(DC API利用時)</t>
         </is>
@@ -3159,7 +3162,7 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="D63" s="33" t="inlineStr">
+      <c r="D63" s="34" t="inlineStr">
         <is>
           <t>条件付き</t>
         </is>
@@ -3206,7 +3209,7 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="D64" s="33" t="inlineStr">
+      <c r="D64" s="34" t="inlineStr">
         <is>
           <t>条件付き</t>
         </is>
@@ -3450,7 +3453,7 @@
           <t>cnf.jwk による Holder Binding 鍵提供</t>
         </is>
       </c>
-      <c r="B70" s="32" t="inlineStr">
+      <c r="B70" s="33" t="inlineStr">
         <is>
           <t>必須(該当時)</t>
         </is>
@@ -3911,7 +3914,7 @@
           <t>追加ハッシュアルゴリズムの mandate</t>
         </is>
       </c>
-      <c r="B81" s="28" t="inlineStr">
+      <c r="B81" s="29" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
